--- a/docs/filter_options_review_2026-09-09.xlsx
+++ b/docs/filter_options_review_2026-09-09.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업력" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연령" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업종" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="target_age_groups" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="business_age_condition" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2131,4 +2133,206 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>target_age_groups 값 (DB 실측, 중복 제거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>만 15세 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>만 19세 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>만 19세~39세</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>만 20세 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>만 20세 이상 ~ 만 39세 이하</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>만 34세 이하</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>만 39세 이하</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>만 40세 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>만 45세 이하</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>전연령</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>business_age_condition 값 (DB 실측, 중복 제거)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>업력무관</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>예비창업자</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>예비창업자~10년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>예비창업자~1년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>예비창업자~3년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>예비창업자~5년미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>예비창업자~7년미만</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>